--- a/TOP_Code_Lookup.xlsx
+++ b/TOP_Code_Lookup.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +106,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,6 +484,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +518,11 @@
           <t>Notes (Typical Courses/Credentials)</t>
         </is>
       </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>CCC SW Sector</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -538,6 +553,11 @@
           <t>AP exams and general education credit mapped to Cal-GETC areas</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -568,6 +588,11 @@
           <t>Biology courses (BIO, BIOLOGY)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Life Sciences/Biotechnology</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -598,6 +623,11 @@
           <t>AP Environmental Science, Biology electives</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -628,6 +658,11 @@
           <t>Business communications (BUS, BUSAD)</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -658,6 +693,11 @@
           <t>Accounting courses (ACCT, ACC)</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -688,6 +728,11 @@
           <t>Introduction to Business (BUSE, BUS)</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -718,6 +763,11 @@
           <t>Business management credentials (BUS, CIS)</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -748,6 +798,11 @@
           <t>Banking and financial management (MAG)</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -778,6 +833,11 @@
           <t>Small business and entrepreneurship (ENP, BUS)</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -808,6 +868,11 @@
           <t>Advertising and marketing (MKT, BUS)</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -838,6 +903,11 @@
           <t>Real estate courses (REALST, REAL ES)</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -868,6 +938,11 @@
           <t>Office technology (CABT, CBTE, CAT)</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -898,6 +973,11 @@
           <t>Journalism and photojournalism (JAMS, PHTO)</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -928,6 +1008,11 @@
           <t>Film/TV production (RTVF, DM)</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -958,6 +1043,11 @@
           <t>Digital video and film production (MULT, MEDIART)</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -988,6 +1078,11 @@
           <t>Computer graphics and social media (CMPGR, DM)</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1018,6 +1113,11 @@
           <t>Video editing and game design (MULT, RTVF)</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1048,6 +1148,11 @@
           <t>Web design and development (WEBD, DM)</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1078,6 +1183,11 @@
           <t>Visual communication and graphic design (MULT, ARTGD)</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1108,6 +1218,11 @@
           <t>Intro to computer science (CSCI, CISC, IS)</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1138,6 +1253,11 @@
           <t>CompTIA A+ and hardware support (CIS)</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1168,6 +1288,11 @@
           <t>C/C++ programming (CSC, COMPSCI)</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1198,6 +1323,11 @@
           <t>AP Computer Science (CMPR, CS)</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1228,6 +1358,11 @@
           <t>Microsoft Office and Linux certifications (CIS, CISC)</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1258,6 +1393,11 @@
           <t>Database and cloud certifications (CIS)</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1288,6 +1428,11 @@
           <t>Cybersecurity analysis — CompTIA CySA+ (CIS)</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1318,6 +1463,11 @@
           <t>IT networking and CompTIA certs (INWT, CIS)</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1348,6 +1498,11 @@
           <t>Cybersecurity — CompTIA Security+ (CNIT, CIS)</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1378,6 +1533,11 @@
           <t>Network security (INWT, CIS, CISHDSP)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1408,6 +1568,11 @@
           <t>Teaching preparation and field experience (EDUC)</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1438,6 +1603,11 @@
           <t>Fitness and firefighter physical ed (FT, PE)</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1468,6 +1638,11 @@
           <t>Exercise science and kinesiology (EXSC)</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1498,6 +1673,11 @@
           <t>American Sign Language I (ASL)</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1528,6 +1708,11 @@
           <t>American Sign Language II (ASL)</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1558,6 +1743,11 @@
           <t>Engineering design (ENGR)</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -1588,6 +1778,11 @@
           <t>Engineering graphics and AutoCAD (EGTECH, ETECH)</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1618,6 +1813,11 @@
           <t>DC/AC electronics (ELTEC, ELDT)</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -1648,6 +1848,11 @@
           <t>Cisco CCNA certification (MICROTK)</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1678,6 +1883,11 @@
           <t>FCC License and telecommunications (ETNTLGY)</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -1708,6 +1918,11 @@
           <t>Industrial electrical (IET)</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1738,6 +1953,11 @@
           <t>Graphic communications and printing (GC)</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1768,6 +1988,11 @@
           <t>Furniture manufacturing technology (FMT)</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1798,6 +2023,11 @@
           <t>HVAC/Refrigeration (HVAC/R, AIRE)</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -1828,6 +2058,11 @@
           <t>Sustainable construction and green building (CEM)</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -1858,6 +2093,11 @@
           <t>ASE automotive certifications (AUTO, AT, ATEC)</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -1888,6 +2128,11 @@
           <t>Auto collision repair and I-CAR (AUBDY, AUTOCOR)</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -1918,6 +2163,11 @@
           <t>Pre-apprenticeship and construction (PREAPP, CNSTR)</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -1948,6 +2198,11 @@
           <t>IBEW electrical apprenticeship (ELE, ELTEC)</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1978,6 +2233,11 @@
           <t>CAD/SolidWorks drafting (DFT, DRAFT, DR)</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2008,6 +2268,11 @@
           <t>Civil engineering drafting (DRAFT)</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2038,6 +2303,11 @@
           <t>CNC and machine shop (MAN, MFET, MFG)</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2068,6 +2338,11 @@
           <t>OSHA standards and industrial maintenance (MSCNC, MAN)</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2098,6 +2373,11 @@
           <t>AWS welding certifications (WEL, WELD)</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2128,6 +2408,11 @@
           <t>Construction fundamentals (CEM)</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2158,6 +2443,11 @@
           <t>AP Art — studio and 3D (ART, AHS)</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2188,6 +2478,11 @@
           <t>Drawing and painting (ART, ARTS)</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2218,6 +2513,11 @@
           <t>General music courses (MUS, MUSI, MUSIC)</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -2248,6 +2548,11 @@
           <t>Music technology and recording (MUS)</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2278,6 +2583,11 @@
           <t>Stagecraft and technical theater (DRAM, TECTHTR, THEA)</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -2308,6 +2618,11 @@
           <t>Theater performance (THEA)</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2338,6 +2653,11 @@
           <t>Dance performance and choreography (DANC)</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -2368,6 +2688,11 @@
           <t>Art photography (ART)</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2398,6 +2723,11 @@
           <t>Commercial and digital photography (AP, PHOT)</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -2428,6 +2758,11 @@
           <t>Graphic design (ART, GD, MAD)</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -2458,6 +2793,11 @@
           <t>Digital fabrication for studio arts (ART)</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -2488,6 +2828,11 @@
           <t>AP and college-level French (FR, FREN)</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2518,6 +2863,11 @@
           <t>AP and college-level Italian (ITA, ITAL)</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -2548,6 +2898,11 @@
           <t>Spanish language (SPAN, SPA)</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -2578,6 +2933,11 @@
           <t>AP and college-level Chinese (CHI)</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -2608,6 +2968,11 @@
           <t>AP and college-level Japanese (JA)</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -2638,6 +3003,11 @@
           <t>General intro to languages and computing (ARAB, CISC)</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -2668,6 +3038,11 @@
           <t>Portuguese language (PORT)</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -2698,6 +3073,11 @@
           <t>Allied health and EMT (ALD HTH, EMT)</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -2728,6 +3108,11 @@
           <t>Medical terminology and health admin (MEDT, MEDA)</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -2758,6 +3143,11 @@
           <t>Medical assisting (MA)</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -2788,6 +3178,11 @@
           <t>Pharmacy technician (PHT, PHAR)</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -2818,6 +3213,11 @@
           <t>Licensed vocational nursing (NRN)</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -2848,6 +3248,11 @@
           <t>Registered nursing (NURS, NURSE, NS)</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -2878,6 +3283,11 @@
           <t>Nurse assistant training (HS)</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -2908,6 +3318,11 @@
           <t>Dental assisting (DEN AST)</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -2938,6 +3353,11 @@
           <t>Dental hygiene (DEN HY)</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -2968,6 +3388,11 @@
           <t>Paramedicine and EMT (EMGM, EMT, EMER)</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -2998,6 +3423,11 @@
           <t>EMS and trauma (EMTP, EMS)</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -3028,6 +3458,11 @@
           <t>Kinesiology and fire fitness (KINS, KINE)</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3058,6 +3493,11 @@
           <t>Child development (CDE, CHIL)</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -3088,6 +3528,11 @@
           <t>Culinary arts and hospitality (CULART, HOSP, CACM)</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3118,6 +3563,11 @@
           <t>Culinary arts advanced and hospitality mgmt (CULART, HCTM)</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -3148,6 +3598,11 @@
           <t>Paralegal and legal procedures (PARA)</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -3178,6 +3633,11 @@
           <t>English composition (ENG, ENGL, ENGLISH)</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -3208,6 +3668,11 @@
           <t>English lit and public speaking (COMM, ENGL)</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -3238,6 +3703,11 @@
           <t>Reading courses (READ)</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -3268,6 +3738,11 @@
           <t>Mathematics and statistics (MATH, MAT, STAT)</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -3298,6 +3773,11 @@
           <t>Chemistry (CHEM, CHE)</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -3328,6 +3808,11 @@
           <t>Geology (GEOL)</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -3358,6 +3843,11 @@
           <t>Psychology (PSYCH, PSYC, PSY)</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -3388,6 +3878,11 @@
           <t>Human services (HUMSR, HS)</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -3418,6 +3913,11 @@
           <t>POST Basic Academy and corrections (ADJ)</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -3448,6 +3948,11 @@
           <t>Homeland security (HLS)</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -3478,6 +3983,11 @@
           <t>Fire technology — rescue and operations (FIPT, FIRE)</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -3508,6 +4018,11 @@
           <t>Fire technology — officer certification (FIPT, FIRE)</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -3538,6 +4053,11 @@
           <t>Fire fitness and physical testing (FIT, FIPT, FOT)</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -3568,6 +4088,11 @@
           <t>Anthropology (ANTHR, ANTH)</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -3598,6 +4123,11 @@
           <t>History (HIS, HIST)</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -3628,6 +4158,11 @@
           <t>Geography and human geography (GEG, GEOG)</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -3658,6 +4193,11 @@
           <t>GIS and mapping technology (GISG, GEOG)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -3688,6 +4228,11 @@
           <t>Sociology (SOC, SOCIO)</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -3718,6 +4263,11 @@
           <t>Barbering and cosmetology (COSM)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -3748,6 +4298,11 @@
           <t>Counseling (COUN)</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -3778,6 +4333,11 @@
           <t>College success skills (COLSK)</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -3808,6 +4368,11 @@
           <t>ESL courses (ESL)</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -3838,6 +4403,11 @@
           <t>General apprenticeship work experience (APP, ALD HTH)</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -3868,6 +4438,11 @@
           <t>FAA Airframe and Powerplant (AERO)</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -3898,6 +4473,11 @@
           <t>Mechanical technology (AGM)</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -3928,6 +4508,11 @@
           <t>Agribusiness management (AGEC)</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -3958,6 +4543,11 @@
           <t>Agriculture leadership (AG)</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -3988,6 +4578,11 @@
           <t>Substance abuse counseling (HS, ASHS — CCAPP/CADTP)</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -4018,6 +4613,11 @@
           <t>Advanced automotive — hybrid/electric (AUTO)</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -4048,6 +4648,11 @@
           <t>Anatomy and physiology (ANAT, BIOL, PHYSO)</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Life Sciences/Biotechnology</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -4078,6 +4683,11 @@
           <t>Animal science (ANSC)</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -4108,6 +4718,11 @@
           <t>Dental and kinesiology health (KIN, LFGD)</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -4138,6 +4753,11 @@
           <t>Architecture and design (ARCH, ARC)</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -4168,6 +4788,11 @@
           <t>Hmong language (HMNG)</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -4198,6 +4823,11 @@
           <t>Astronomy (ASTR, ASTRON)</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -4228,6 +4858,11 @@
           <t>FAA Airframe certification (AERO)</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -4258,6 +4893,11 @@
           <t>Aviation maintenance technology (AVIATEK)</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -4288,6 +4928,11 @@
           <t>Biotechnology (BIOL)</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Life Sciences/Biotechnology</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -4318,6 +4963,11 @@
           <t>Broadcasting and podcasting (RTVF, JOURN)</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -4348,6 +4998,11 @@
           <t>Carpentry apprenticeship (ACA)</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -4378,6 +5033,11 @@
           <t>Humanities — CLEP (HUM)</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -4408,6 +5068,11 @@
           <t>Digital media/graphic design (ARTG)</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -4438,6 +5103,11 @@
           <t>Community health work (HS)</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -4468,6 +5138,11 @@
           <t>Construction inspection (INSPEC)</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -4498,6 +5173,11 @@
           <t>POST Peace Officer training (ADJ, ADM JUS, CRIM)</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -4528,6 +5208,11 @@
           <t>Dairy management (ANSC)</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -4558,6 +5243,11 @@
           <t>Diagnostic medical sonography (DMS)</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -4588,6 +5278,11 @@
           <t>Diesel and truck technology (DIESLTK)</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -4618,6 +5313,11 @@
           <t>Dietary management and nutrition (NUTR)</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -4648,6 +5348,11 @@
           <t>Advanced carpentry/print reading (ACA)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -4678,6 +5383,11 @@
           <t>E-commerce business (BUS)</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -4708,6 +5418,11 @@
           <t>Economics — AP and college level (ECO, ECON)</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -4738,6 +5453,11 @@
           <t>Universal design for learning (EDUC)</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -4768,6 +5488,11 @@
           <t>Continuing education teacher training (CE)</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -4798,6 +5523,11 @@
           <t>Environmental conservation (ENSCI, ENV SCI, ENVIR)</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -4828,6 +5558,11 @@
           <t>Water resources and environment (ENSCI)</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -4858,6 +5593,11 @@
           <t>Hazardous materials first responder (FST)</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -4888,6 +5628,11 @@
           <t>African American studies (ETH S)</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -4918,6 +5663,11 @@
           <t>Fashion and apparel construction (FASH, FDM)</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -4948,6 +5698,11 @@
           <t>Sewing and fashion design (FDM)</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -4978,6 +5733,11 @@
           <t>Film studies (FILM)</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -5008,6 +5768,11 @@
           <t>Art history (ART, ARTH)</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -5038,6 +5803,11 @@
           <t>Aviation passenger services (ATC)</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -5068,6 +5838,11 @@
           <t>Floral art and design (EHS, PLNT SC)</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -5098,6 +5873,11 @@
           <t>Administration of justice (ADJ, CJ, ADJU)</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -5128,6 +5908,11 @@
           <t>German language (GER)</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -5158,6 +5943,11 @@
           <t>Personal health and wellness (HES, HE)</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -5188,6 +5978,11 @@
           <t>Medical terminology articulation (HEOC)</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -5218,6 +6013,11 @@
           <t>Hebrew language (HEBR)</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -5248,6 +6048,11 @@
           <t>Horticulture and permaculture (HORT)</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -5278,6 +6083,11 @@
           <t>Hospitality and tourism (HOSP, FN, CUL)</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -5308,6 +6118,11 @@
           <t>OSHA construction safety (AGM, AMW, IET)</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -5338,6 +6153,11 @@
           <t>Infant/child development (ECE, CLDV)</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -5368,6 +6188,11 @@
           <t>Interior design and LEED (ID)</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -5398,6 +6223,11 @@
           <t>Counseling and guidance (COUN)</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -5428,6 +6258,11 @@
           <t>Korean language (KOR)</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -5458,6 +6293,11 @@
           <t>Landscape design (EHS, HORT)</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -5488,6 +6328,11 @@
           <t>Protective services (SPS)</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -5518,6 +6363,11 @@
           <t>Logistics and transportation management (BUSMGT, LOGST)</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -5548,6 +6398,11 @@
           <t>Marine technology — boatworks (APMT)</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -5578,6 +6433,11 @@
           <t>Carpentry/drywall apprenticeship (ACA)</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -5608,6 +6468,11 @@
           <t>Medical terminology and health info (HLH, MOA, CIT)</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -5638,6 +6503,11 @@
           <t>Microbiology (MICRO)</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Life Sciences/Biotechnology</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -5668,6 +6538,11 @@
           <t>Millwrighting apprenticeship (AMW)</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -5698,6 +6573,11 @@
           <t>Funeral/mortuary science (MORT)</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -5728,6 +6608,11 @@
           <t>Environmental health (ENVHR)</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -5758,6 +6643,11 @@
           <t>Foods and nutrition (CULN, NUTR, FN)</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -5788,6 +6678,11 @@
           <t>Occupational therapy assistant (OTA)</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -5818,6 +6713,11 @@
           <t>Persian language (PRSN)</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
@@ -5848,6 +6748,11 @@
           <t>Cisco CCNA networking certification (CNIT)</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -5878,6 +6783,11 @@
           <t>Physical education and self-defense (PEC, KIN)</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -5908,6 +6818,11 @@
           <t>AP Physics C and college physics (PHYSICS, PHYS)</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -5938,6 +6853,11 @@
           <t>AP Physics 1 and 2 — algebra-based (PHY, PHYS)</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
@@ -5968,6 +6888,11 @@
           <t>Private pilot — FAA certificate (AVIA, AERO)</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -5998,6 +6923,11 @@
           <t>Berry production and plant science (HORT, PLNT SC)</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
@@ -6028,6 +6958,11 @@
           <t>POST peace officer certification (ADJ, ADJU)</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -6058,6 +6993,11 @@
           <t>Political science and government (POLS, POL)</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -6088,6 +7028,11 @@
           <t>Child literacy development (ECE)</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -6118,6 +7063,11 @@
           <t>Radiologic technology (RT)</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -6148,6 +7098,11 @@
           <t>Marine craftsmanship — boatworks (APMT)</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -6178,6 +7133,11 @@
           <t>Sheet metal and installation (SM, AIRC, IWAP)</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Energy, Construction &amp; Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -6208,6 +7168,11 @@
           <t>Statistics — AP (SOC/cross-listed)</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -6238,6 +7203,11 @@
           <t>Accessible media and IT (CBTE, CIS, CAT)</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -6268,6 +7238,11 @@
           <t>Tourism (TOUR)</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Retail, Hospitality &amp; Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -6298,6 +7273,11 @@
           <t>Commercial driver's license (TD)</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Advanced Transportation &amp; Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -6328,6 +7308,11 @@
           <t>Veterinary science (ANSC)</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -6358,6 +7343,11 @@
           <t>Vietnamese language (VIET)</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Academic Transfer &amp; General Education</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
@@ -6388,6 +7378,11 @@
           <t>Wine and hospitality (CAHM)</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -6418,6 +7413,11 @@
           <t>Water and wastewater technology (WST)</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Agriculture, Water &amp; Environmental Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
@@ -6446,6 +7446,11 @@
       <c r="F199" s="5" t="inlineStr">
         <is>
           <t>Digital media and graphic arts (ARTG)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ICT/Digital Media</t>
         </is>
       </c>
     </row>
